--- a/docs/gantt.xlsx
+++ b/docs/gantt.xlsx
@@ -379,7 +379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -396,6 +396,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -480,7 +481,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Занятие 3 / пары 9–10</t>
+          <t>Занятие 3</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -490,17 +491,44 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Файлы данных БД (10 CSV в db/import), ER-диаграмма и скрипт создания БД</t>
+          <t>Проектирование БД: CSV из импорта, ER-диаграмма, модель vozduh.mwb</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Текущий этап</t>
+          <t>Завершено</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Занятие 4</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>11–12</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Реализация БД: create_v1.sql, data.sql, queries.sql; глава отчёта «Проектирование БД»</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Завершено</t>
         </is>
       </c>
     </row>
